--- a/backend/output/Summary.xlsx
+++ b/backend/output/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,61 +436,169 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Employee Count</t>
+          <t>Total Basic Pay</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Gross Wages Total</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>EE Share Total</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ER Share Total</t>
+          <t>Total EPF (EE Share)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Feb 2024</t>
+          <t>Apr08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>151723</v>
       </c>
       <c r="C2" t="n">
-        <v>81500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3900</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1195</v>
+        <v>18206</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jan 2024</t>
+          <t>Aug08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>199891</v>
       </c>
       <c r="C3" t="n">
-        <v>79000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3900</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1195</v>
+        <v>23984</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dec08</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>227677</v>
+      </c>
+      <c r="C4" t="n">
+        <v>27318</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Feb09</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>242339</v>
+      </c>
+      <c r="C5" t="n">
+        <v>29078</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jan09</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>240210</v>
+      </c>
+      <c r="C6" t="n">
+        <v>28822</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jul08</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>184347</v>
+      </c>
+      <c r="C7" t="n">
+        <v>22120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jun08</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>183350</v>
+      </c>
+      <c r="C8" t="n">
+        <v>22001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mar09</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>247914</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29747</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>May08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>164212</v>
+      </c>
+      <c r="C10" t="n">
+        <v>19705</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nov08</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>226082</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27127</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Oct08</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>222942</v>
+      </c>
+      <c r="C12" t="n">
+        <v>26750</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sep08</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>203212</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24383</v>
       </c>
     </row>
   </sheetData>
